--- a/01_Full_Design/Project Outputs for DA1_prj/DA1_prj.xlsx
+++ b/01_Full_Design/Project Outputs for DA1_prj/DA1_prj.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nghuy\OneDrive\Máy tính\ALTIUM-PROJECT\3_DA1_prj\Project Outputs for DA1_prj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B74A1ADC-FBAA-4692-A77C-B54F33B4EE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2D48603-A3EF-4152-BD08-AE212CB0CCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="4020" windowWidth="21600" windowHeight="11295" xr2:uid="{68319A8D-8E38-4BEB-9338-60594CA0C7F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1D506B58-8869-44E0-9663-22213BBA0FED}"/>
   </bookViews>
   <sheets>
     <sheet name="DA1_prj" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="157">
   <si>
     <t>Line #</t>
   </si>
@@ -53,16 +56,28 @@
     <t>Designator</t>
   </si>
   <si>
+    <t>Revision ID</t>
+  </si>
+  <si>
+    <t>Revision State</t>
+  </si>
+  <si>
+    <t>Revision Status</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
     <t>Footprint</t>
   </si>
   <si>
-    <t>Manufacturer</t>
-  </si>
-  <si>
-    <t>Manufacturer Part Number</t>
+    <t>Manufacturer 1</t>
+  </si>
+  <si>
+    <t>Manufacturer Part Number 1</t>
+  </si>
+  <si>
+    <t>Manufacturer Lifecycle 1</t>
   </si>
   <si>
     <t>Supplier 1</t>
@@ -77,226 +92,340 @@
     <t>Supplier Subtotal 1</t>
   </si>
   <si>
+    <t>3002</t>
+  </si>
+  <si>
+    <t>Battery Holder: SMT, 1 Coin Cell, 20mm, PhosBronze/Tin-Nickel | Keystone Electronics 3002</t>
+  </si>
+  <si>
+    <t>BT1</t>
+  </si>
+  <si>
+    <t>Not managed</t>
+  </si>
+  <si>
+    <t>BAT_3002</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>10uF/16V</t>
-  </si>
-  <si>
-    <t>CAPP</t>
-  </si>
-  <si>
-    <t>C1, C4, C5</t>
-  </si>
-  <si>
-    <t>CAPC2012X140N</t>
-  </si>
-  <si>
-    <t>10uF/10V</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>0.1uF/10V</t>
-  </si>
-  <si>
-    <t>CAPC</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>tu 0402</t>
-  </si>
-  <si>
-    <t>0.1uF/6.3V</t>
-  </si>
-  <si>
-    <t>C6, C7, C11, C12, C15, C20, C21, C22, C23, C24, C25, C26, C27, C28, C29, C30, C31, C36, C37, C38, C39, C40, C41, C42, C43, C46, C47, C48, C51, C52, C53, C54, C55</t>
-  </si>
-  <si>
-    <t>4.7 µF ±20% 6.3V Ceramic Capacitor X7T 0402 (1005 Metric): GRT155D70J475ME13J</t>
-  </si>
-  <si>
-    <t>C8, C9, C10</t>
-  </si>
-  <si>
-    <t>4.7uF/6.3V</t>
-  </si>
-  <si>
-    <t>C13, C14, C18</t>
-  </si>
-  <si>
-    <t>C16, C17, C44, C45</t>
-  </si>
-  <si>
-    <t>CAPC1608X90</t>
-  </si>
-  <si>
-    <t>10uF/6.3V</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>16pF/6.3V</t>
-  </si>
-  <si>
-    <t>C32, C33, C49, C50</t>
-  </si>
-  <si>
-    <t>C34</t>
-  </si>
-  <si>
-    <t>1uF/6.3V</t>
-  </si>
-  <si>
-    <t>C35</t>
-  </si>
-  <si>
-    <t>150060YS75000</t>
-  </si>
-  <si>
-    <t>LED YELLOW CLEAR 0603 SMD</t>
-  </si>
-  <si>
-    <t>D1, D2</t>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>Capacitor (Semiconductor SIM Model)</t>
+  </si>
+  <si>
+    <t>C1, C2, C4, C5, C7, C8, C25, C33, C34, C35, C36</t>
+  </si>
+  <si>
+    <t>FP-C0603C-CF-IPC_A</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
+    <t>C3, C6, C9</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>C10, C11, C15, C17, C19, C21, C23</t>
+  </si>
+  <si>
+    <t>10pF</t>
+  </si>
+  <si>
+    <t>C12, C24</t>
+  </si>
+  <si>
+    <t>4,7pF</t>
+  </si>
+  <si>
+    <t>C13, C26</t>
+  </si>
+  <si>
+    <t>10nF</t>
+  </si>
+  <si>
+    <t>C14, C16, C18, C20, C22, C27, C28, C29, C30, C31, C32</t>
+  </si>
+  <si>
+    <t>PESD5V0L2BT,215</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>SOT95P230X110-3N</t>
+  </si>
+  <si>
+    <t>BZX84C3V6LT1G</t>
+  </si>
+  <si>
+    <t>D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D16, D17, D18, D19, D20, D21, D22, D23</t>
+  </si>
+  <si>
+    <t>SOT95P240X111-3N</t>
+  </si>
+  <si>
+    <t>B560C-13-F</t>
+  </si>
+  <si>
+    <t>Diode Schottky 60 V 5A Surface Mount SMC</t>
+  </si>
+  <si>
+    <t>D24</t>
+  </si>
+  <si>
+    <t>SMC</t>
+  </si>
+  <si>
+    <t>LED_USB_RX_TX</t>
+  </si>
+  <si>
+    <t>430mcd Colorless transparence 520nm Emerald 140° LED0603 Light Emitting Diodes (LED) ROHS</t>
+  </si>
+  <si>
+    <t>D25</t>
   </si>
   <si>
     <t>WL-SMCW_0603_150060xx75000</t>
   </si>
   <si>
-    <t>JP2</t>
-  </si>
-  <si>
-    <t>WR-PHD 2.54 mm Angled Socket Header</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>JP2-D1T</t>
-  </si>
-  <si>
-    <t>W¨¹rth Elektronik eiSos GmbH</t>
-  </si>
-  <si>
-    <t>USB_micro</t>
-  </si>
-  <si>
-    <t>No Description Available</t>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>47346-0001_MOL</t>
+    <t>LED_CAN_RX_TX</t>
+  </si>
+  <si>
+    <t>D26</t>
+  </si>
+  <si>
+    <t>LED_ERROR</t>
+  </si>
+  <si>
+    <t>D27</t>
+  </si>
+  <si>
+    <t>0ZCH0150FF2E</t>
+  </si>
+  <si>
+    <t>1210 SMT PPTC | 1.50 Ih | 6V</t>
+  </si>
+  <si>
+    <t>F1, F2, F3, F4, F5, F6, F7, F8, F9, F10, F11, F12, F13, F14, F15, F16, F17, F18, F19, F20, F21, F22, F23, F24, F25, F26, F27, F28, F29, F30</t>
+  </si>
+  <si>
+    <t>FUSC3225X90N</t>
+  </si>
+  <si>
+    <t>MountingHole_Pad</t>
+  </si>
+  <si>
+    <t>H1, H2, H3, H4</t>
+  </si>
+  <si>
+    <t>MountingHole_2.7mm_M2.5_DIN965_Pad</t>
   </si>
   <si>
     <t>JP8</t>
   </si>
   <si>
-    <t>J3, J5</t>
-  </si>
-  <si>
-    <t>JP8-C1T</t>
-  </si>
-  <si>
-    <t>J4</t>
-  </si>
-  <si>
-    <t>10uH/250mA</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>L-SMD-M-12x10</t>
-  </si>
-  <si>
-    <t>Wurth Elektronik</t>
-  </si>
-  <si>
-    <t>1K</t>
+    <t>Connector 8</t>
+  </si>
+  <si>
+    <t>JP1</t>
+  </si>
+  <si>
+    <t>HDR/Header/8</t>
+  </si>
+  <si>
+    <t>Screw_terminal 1x6</t>
+  </si>
+  <si>
+    <t>Header, 6-Pin</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>HDR/Terminal/6</t>
+  </si>
+  <si>
+    <t>_x0016_Screw_terminal 1x6</t>
+  </si>
+  <si>
+    <t>P2, P3, P6, P7, P8, P11</t>
+  </si>
+  <si>
+    <t>_x0016_Screw_terminal 1x3</t>
+  </si>
+  <si>
+    <t>Header, 3-Pin</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>HDR/Terminal/3</t>
+  </si>
+  <si>
+    <t>_x0016_Screw_terminal 1x4</t>
+  </si>
+  <si>
+    <t>Header, 4-Pin</t>
+  </si>
+  <si>
+    <t>P5, P10</t>
+  </si>
+  <si>
+    <t>HDR/Terminal/4</t>
+  </si>
+  <si>
+    <t>_x0016_Screw_terminal 1x2</t>
+  </si>
+  <si>
+    <t>Header, 2-Pin</t>
+  </si>
+  <si>
+    <t>P9, P12</t>
+  </si>
+  <si>
+    <t>HDR/Terminal/2</t>
+  </si>
+  <si>
+    <t>BUK9M15-60EX</t>
+  </si>
+  <si>
+    <t>Bá»™ chuyá»ƒn Ä‘á»•i N-Channel 60 V 47A (Tc) 75W (Tc) gáº¯n bá» máº·t LFPAK33</t>
+  </si>
+  <si>
+    <t>Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+  </si>
+  <si>
+    <t>TRANS_BUK9M15-60EX</t>
+  </si>
+  <si>
+    <t>BC847C-QR</t>
+  </si>
+  <si>
+    <t>Q9, Q10, Q11</t>
+  </si>
+  <si>
+    <t>1,5k</t>
   </si>
   <si>
     <t>RES</t>
   </si>
   <si>
-    <t>R1, R2</t>
+    <t>R1</t>
   </si>
   <si>
     <t>tro smd 0603</t>
   </si>
   <si>
-    <t>4.7k</t>
-  </si>
-  <si>
-    <t>R3, R4, R5</t>
-  </si>
-  <si>
-    <t>0R/DNP</t>
-  </si>
-  <si>
-    <t>RES SMD 12K OHM 1% 1/10W 0603, P/N: ERJ-3EKF1202V</t>
-  </si>
-  <si>
-    <t>R6, R7</t>
+    <t>2k</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>R3, R5</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>R4, R6</t>
+  </si>
+  <si>
+    <t>1k</t>
+  </si>
+  <si>
+    <t>R7, R8, R9, R10, R11, R12, R13, R14, R15, R16, R17, R18, R19, R20, R21, R22, R23, R24, R25, R26, R63, R64, R65, R66, R67, R68, R69, R70, R71, R72, R73, R74, R75, R76, R77, R78, R79, R80, R81, R82</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>R27, R28, R29, R33, R34, R35, R39, R40, R43, R44, R45, R46, R47, R48, R49, R50, R51, R52, R53, R54, R55, R56, R57, R58, R59, R60, R61, R62, R83, R84, R85, R86, R87, R88, R89, R90, R91, R92, R93, R94, R95, R96, R97, R98, R99, R100, R101, R102, R103, R104, R105, R106, R109, R110, R118</t>
   </si>
   <si>
     <t>10k</t>
   </si>
   <si>
-    <t>RES 4.7K OHM 1% 1/10W 0603, P/N: ERJ-U03F4701V</t>
-  </si>
-  <si>
-    <t>R8, R9, R10, R11, R12, R13</t>
-  </si>
-  <si>
-    <t>R14, R18</t>
-  </si>
-  <si>
-    <t>22R</t>
-  </si>
-  <si>
-    <t>R15, R16</t>
-  </si>
-  <si>
-    <t>R17</t>
-  </si>
-  <si>
-    <t>LMS1587ISX-3.3/NOPB</t>
-  </si>
-  <si>
-    <t>3-A, 13-V, linear voltage regulator</t>
+    <t>R30, R31, R32, R36, R37, R38, R41, R42, R107, R108, R111, R112, R113, R114, R115, R116, R117, R119, R120, R121</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>R122, R123, R124</t>
+  </si>
+  <si>
+    <t>ST-Link V2 connector</t>
+  </si>
+  <si>
+    <t>STLINK2</t>
+  </si>
+  <si>
+    <t>HDR/Header/6</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>Switch button 2 pin</t>
+  </si>
+  <si>
+    <t>SW1</t>
+  </si>
+  <si>
+    <t>SW1-SMD</t>
+  </si>
+  <si>
+    <t>4-5435640-1</t>
+  </si>
+  <si>
+    <t>SWITCH ROCKER DIP SPST 60MA 5V</t>
+  </si>
+  <si>
+    <t>SW2</t>
+  </si>
+  <si>
+    <t>Unknown server</t>
+  </si>
+  <si>
+    <t>FP-4-5435640-1-MFG</t>
+  </si>
+  <si>
+    <t>MIC5504-3.3YM5_TR</t>
+  </si>
+  <si>
+    <t>Linear Voltage Regulator IC Positive Fixed 1 Output 300mA SOT-23-5</t>
   </si>
   <si>
     <t>U1</t>
   </si>
   <si>
-    <t>TO254P1524X483-4N</t>
-  </si>
-  <si>
-    <t>TPS7A4533DCQR</t>
-  </si>
-  <si>
-    <t>Single Output Fast Transient Response LDO, 1.5 A, Fixed 3.3 V Output, 2.1 to 20 V Input, 6-pin SOT-223 (DCQ), -40 to 125 degC, Green (RoHS &amp; no Sb/Br)</t>
+    <t>SOT95P280X145-5N</t>
+  </si>
+  <si>
+    <t>STM32F373VBTx</t>
   </si>
   <si>
     <t>U2</t>
   </si>
   <si>
-    <t>DCQ0006A_M</t>
-  </si>
-  <si>
-    <t>Texas Instruments</t>
-  </si>
-  <si>
-    <t>ISO7721DR</t>
-  </si>
-  <si>
-    <t>Robust EMC, dual-channel, 1/1, reinforced digital isolator</t>
+    <t>QFP50P1600X1600X160-100N</t>
+  </si>
+  <si>
+    <t>TCAN332D</t>
+  </si>
+  <si>
+    <t>3.3-V CAN Transceivers</t>
   </si>
   <si>
     <t>U3</t>
@@ -305,67 +434,85 @@
     <t>SOIC127P599X175-8N</t>
   </si>
   <si>
-    <t>STM32H745ZIT3</t>
-  </si>
-  <si>
-    <t>HIGH-PERFORMANCE AND DSP WITH DP</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>FP-LQFP144-1A-MFG</t>
-  </si>
-  <si>
-    <t>STMicroelectronics</t>
-  </si>
-  <si>
-    <t>STM32H745ZIT6</t>
-  </si>
-  <si>
-    <t>MTFC32GAZAQDW-AAT</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
-    <t>SOIC127P602X173-8N - duplicate</t>
-  </si>
-  <si>
-    <t>OPA2340UA</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>SOIC127P602X173-8</t>
-  </si>
-  <si>
-    <t>ATMEGA324PA</t>
-  </si>
-  <si>
-    <t>U7</t>
-  </si>
-  <si>
-    <t>QFP80P1200X1200X120-44</t>
-  </si>
-  <si>
-    <t>ECS-250-12-33Q-JES-TR</t>
-  </si>
-  <si>
-    <t>25 MHz Â±20ppm Crystal 12pF 40 Ohms 4-SMD, No Lead</t>
+    <t>PC817X3NSZ1B</t>
+  </si>
+  <si>
+    <t>Optoisolator Transistor Output - 1 Channel 4-DIP</t>
+  </si>
+  <si>
+    <t>U4, U5, U6, U7, U8, U9, U10, U11, U12, U13, U14, U15, U16, U17, U18, U19, U20, U21, U22, U23</t>
+  </si>
+  <si>
+    <t>DIP762W50P254L495H455Q4</t>
+  </si>
+  <si>
+    <t>LM324AM</t>
+  </si>
+  <si>
+    <t>Low power general-purpose quad operational amplifier 14-SOIC 0 to 70</t>
+  </si>
+  <si>
+    <t>U24</t>
+  </si>
+  <si>
+    <t>SOIC127P600X175-14N</t>
+  </si>
+  <si>
+    <t>LM2904DR</t>
+  </si>
+  <si>
+    <t>Dual, 26-V, 700-kHz operational amplifier</t>
+  </si>
+  <si>
+    <t>U25</t>
+  </si>
+  <si>
+    <t>SN74HC14N</t>
+  </si>
+  <si>
+    <t>Hex Schmitt-Trigger Inverters, N0014A, TUBE</t>
+  </si>
+  <si>
+    <t>U26, U27</t>
+  </si>
+  <si>
+    <t>N0014A</t>
+  </si>
+  <si>
+    <t>USB-B1HSB6</t>
+  </si>
+  <si>
+    <t>USB-B (USB TYPE-B) - Receptacle Connector 4 Position Through Hole, Right Angle</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>OST_USB-B1HSB6</t>
+  </si>
+  <si>
+    <t>HSE</t>
+  </si>
+  <si>
+    <t>Crystal For all Crystal 2pin.</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>XT3</t>
+  </si>
+  <si>
+    <t>LSE</t>
+  </si>
+  <si>
+    <t>32.768 kHz Â±20ppm Crystal 7pF 70 kOhms 2-SMD, No Lead</t>
   </si>
   <si>
     <t>Y1</t>
   </si>
   <si>
-    <t>XTAL_ECS-250-12-33Q-JES-TR</t>
-  </si>
-  <si>
-    <t>8MHz</t>
-  </si>
-  <si>
-    <t>Y2</t>
+    <t>XTAL_ECS-.327-7-34B-TR</t>
   </si>
 </sst>
 </file>
@@ -761,23 +908,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2030A8D3-A037-46C1-B0B4-602C3889BA7C}">
-  <dimension ref="A1:L34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA59A9FC-380F-4CDD-A4D0-97815A9A02C5}">
+  <dimension ref="A1:P45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
     <col min="3" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
-    <col min="6" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" customWidth="1"/>
-    <col min="10" max="10" width="23.140625" customWidth="1"/>
-    <col min="11" max="11" width="20.85546875" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
+    <col min="11" max="11" width="27.42578125" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" customWidth="1"/>
+    <col min="14" max="14" width="23.140625" customWidth="1"/>
+    <col min="15" max="15" width="20.85546875" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -814,838 +966,1382 @@
       <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1">
-        <v>3</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="H2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="H3" s="1">
+        <v>11</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="H4" s="1">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="1">
-        <v>33</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="H5" s="1">
+        <v>7</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="1">
-        <v>3</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="1">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="1">
-        <v>4</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="E8" s="1"/>
       <c r="F8" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="H8" s="1">
+        <v>11</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="1">
+        <v>37</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="I9" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="1">
-        <v>4</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E10" s="1"/>
       <c r="F10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
         <v>22</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="I10" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="1">
+        <v>44</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="I11" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="1">
+        <v>48</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="I12" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="1">
-        <v>2</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="E13" s="1"/>
       <c r="F13" s="2" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="1">
+        <v>53</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="I14" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="E15" s="1"/>
       <c r="F15" s="2" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="H15" s="1">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="E16" s="1"/>
       <c r="F16" s="2" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="H16" s="1">
+        <v>4</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="1">
+        <v>63</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+      <c r="I17" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="1">
+        <v>67</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1">
         <v>1</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+      <c r="I18" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="1">
-        <v>2</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E19" s="1"/>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="H19" s="1">
+        <v>6</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="1">
-        <v>3</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="E20" s="1"/>
       <c r="F20" s="2" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="1">
+        <v>77</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+      <c r="I21" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="1">
-        <v>6</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="E22" s="1"/>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+      <c r="H22" s="1">
+        <v>2</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="1">
-        <v>2</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="E23" s="1"/>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="H23" s="1">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" s="1">
-        <v>2</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="E24" s="1"/>
       <c r="F24" s="2" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="H24" s="1">
+        <v>3</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="1">
+        <v>91</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1">
         <v>1</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="I25" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="1">
+        <v>94</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1">
         <v>1</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+      <c r="I26" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="B27" s="2" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="E27" s="1"/>
       <c r="F27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1">
+        <v>2</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="B28" s="2" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="E28" s="1"/>
       <c r="F28" s="2" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+      <c r="H28" s="1">
+        <v>2</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E29" s="1"/>
       <c r="F29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1">
+        <v>40</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="B30" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="E30" s="1"/>
       <c r="F30" s="2" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+      <c r="H30" s="1">
+        <v>55</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="B31" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E31" s="1"/>
       <c r="F31" s="2" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="B32" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="E32" s="1"/>
       <c r="F32" s="2" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+      <c r="H32" s="1">
+        <v>3</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E33" s="1">
+        <v>108</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1">
         <v>1</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+      <c r="I33" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" s="1">
+        <v>112</v>
+      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1">
         <v>1</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
+      <c r="I34" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1">
+        <v>20</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1">
+        <v>1</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1">
+        <v>2</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1">
+        <v>1</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1">
+        <v>1</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
